--- a/order_forms/034_material_testing_instrument_order_form--order_forms.xlsx
+++ b/order_forms/034_material_testing_instrument_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Material Testing Instrument Order Form</t>
+          <t>Material Testing Instrument Order Form Page 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Instrument Order Details</t>
+          <t>Instrument Order Details 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>instrument_status</t>
+          <t>instrument_status_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Instrument Status</t>
+          <t>Instrument Status 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -917,7 +917,7 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1248,7 +1248,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>instrument_status_choices</t>
+          <t>instrument_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>instrument_status_choices</t>
+          <t>instrument_status_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>instrument_status_choices</t>
+          <t>instrument_status_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
